--- a/temp/pages/all-profiles.xlsx
+++ b/temp/pages/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-25T16:23:10-04:00</t>
+    <t>2025-07-27T11:31:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -995,7 +995,7 @@
     <t>Observation</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-simple-observation</t>
   </si>
   <si>
     <t>Vital Signs
@@ -1005,10 +1005,7 @@
     <t>assessment observation</t>
   </si>
   <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
-  </si>
-  <si>
-    <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
+    <t>\-</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -1094,7 +1091,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>registered | preliminary | final | amended +</t>
+    <t>(USCDI) registered | preliminary | final | amended +</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -1115,7 +1112,7 @@
     <t>Observation.category</t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
+    <t>(USCDI) Classification of  type of observation</t>
   </si>
   <si>
     <t>A code that classifies the general type of observation being made.</t>
@@ -1127,29 +1124,29 @@
     <t>Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>FHIR and US Core codes for high level observation categories.</t>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Observation.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-simple-observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Observation.category:us-core</t>
-  </si>
-  <si>
-    <t>us-core</t>
-  </si>
-  <si>
-    <t>𝗔𝗗𝗗𝗜𝗧𝗜𝗢𝗡𝗔𝗟 𝗨𝗦𝗖𝗗𝗜: US Core classification of type of observation</t>
-  </si>
-  <si>
-    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1179,23 +1176,17 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group|Device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-location)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
-    <t>Who and/or what the observation is about</t>
+    <t>(USCDI) Who and/or what the observation is about</t>
   </si>
   <si>
     <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
@@ -1257,10 +1248,10 @@
 PeriodTiminginstant</t>
   </si>
   <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g., human patients - this is usually called the "physiologically relevant time".</t>
+    <t>(USCDI) Clinically relevant time/time-period for observation</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time".</t>
   </si>
   <si>
     <t>At least a date should be present unless this observation is a historical report.</t>
@@ -1288,11 +1279,11 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|PractitionerRole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|PractitionerRole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
 </t>
   </si>
   <si>
-    <t>Who is responsible for the observation</t>
+    <t>(USCDI) Who is responsible for the observation</t>
   </si>
   <si>
     <t>Who was responsible for asserting the observed value as "true".</t>
@@ -1308,7 +1299,7 @@
 timedateTimePeriod</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>(USCDI) Actual result</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1407,6 +1398,9 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
@@ -1606,14 +1600,14 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|http://hl7.org/fhir/us/core/StructureDefinition/us-core-documentreference|http://hl7.org/fhir/us/core/StructureDefinition/us-core-questionnaireresponse|ImagingStudy|Media|MolecularSequence)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation)
 </t>
   </si>
   <si>
-    <t>𝗔𝗗𝗗𝗜𝗧𝗜𝗢𝗡𝗔𝗟 𝗨𝗦𝗖𝗗𝗜: US Core Profiles or other resource the observation is made from</t>
-  </si>
-  <si>
-    <t>US Core Observations, DocumentReference, QuestionnaireResponse or other resource from which this observation value is derived.</t>
+    <t>(USCDI) US Core Profiles or other resource the observation is made from</t>
+  </si>
+  <si>
+    <t>Observations or or other resource such as a QuestionnaireResponse from which this observation value is derived.</t>
   </si>
   <si>
     <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
@@ -1653,6 +1647,9 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -2188,7 +2185,7 @@
     <col min="23" max="23" width="13.91796875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="126.94140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="148.8828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="59.63671875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.98046875" customWidth="true" bestFit="true"/>
@@ -7106,7 +7103,7 @@
         <v>314</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -7168,7 +7165,7 @@
         <v>20</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="48">
@@ -7176,10 +7173,10 @@
         <v>303</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7281,10 +7278,10 @@
         <v>303</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7384,10 +7381,10 @@
         <v>303</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7489,10 +7486,10 @@
         <v>303</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7594,10 +7591,10 @@
         <v>303</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7699,10 +7696,10 @@
         <v>303</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7804,10 +7801,10 @@
         <v>303</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7909,10 +7906,10 @@
         <v>303</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8016,10 +8013,10 @@
         <v>303</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8045,14 +8042,14 @@
         <v>137</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>20</v>
@@ -8101,7 +8098,7 @@
         <v>20</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>74</v>
@@ -8121,14 +8118,14 @@
         <v>303</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" t="s" s="2">
@@ -8147,17 +8144,17 @@
         <v>82</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q57" t="s" s="2">
         <v>20</v>
@@ -8206,7 +8203,7 @@
         <v>20</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>74</v>
@@ -8226,14 +8223,14 @@
         <v>303</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" t="s" s="2">
@@ -8252,16 +8249,16 @@
         <v>82</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" t="s" s="2">
@@ -8311,7 +8308,7 @@
         <v>20</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>74</v>
@@ -8331,10 +8328,10 @@
         <v>303</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8360,16 +8357,16 @@
         <v>101</v>
       </c>
       <c r="M59" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="O59" t="s" s="2">
+      <c r="P59" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="Q59" t="s" s="2">
         <v>20</v>
@@ -8397,11 +8394,11 @@
         <v>165</v>
       </c>
       <c r="Z59" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AA59" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AA59" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AB59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8418,7 +8415,7 @@
         <v>20</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>81</v>
@@ -8438,10 +8435,10 @@
         <v>303</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8467,16 +8464,16 @@
         <v>187</v>
       </c>
       <c r="M60" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="O60" t="s" s="2">
+      <c r="P60" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="Q60" t="s" s="2">
         <v>20</v>
@@ -8504,26 +8501,26 @@
         <v>105</v>
       </c>
       <c r="Z60" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AA60" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AA60" t="s" s="2">
+      <c r="AB60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC60" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AD60" s="2"/>
       <c r="AE60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>74</v>
@@ -8543,13 +8540,13 @@
         <v>303</v>
       </c>
       <c r="B61" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="D61" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="E61" t="s" s="2">
         <v>20</v>
@@ -8562,7 +8559,7 @@
         <v>75</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>20</v>
@@ -8574,16 +8571,16 @@
         <v>187</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="N61" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="O61" t="s" s="2">
+      <c r="P61" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="Q61" t="s" s="2">
         <v>20</v>
@@ -8611,10 +8608,10 @@
         <v>165</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AA61" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AB61" t="s" s="2">
         <v>20</v>
@@ -8632,7 +8629,7 @@
         <v>20</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>74</v>
@@ -8652,14 +8649,14 @@
         <v>303</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" t="s" s="2">
@@ -8681,16 +8678,16 @@
         <v>187</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="O62" t="s" s="2">
+      <c r="P62" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="Q62" t="s" s="2">
         <v>20</v>
@@ -8700,29 +8697,27 @@
         <v>20</v>
       </c>
       <c r="T62" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Z62" s="2"/>
+      <c r="AA62" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="U62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AB62" t="s" s="2">
         <v>20</v>
       </c>
@@ -8739,7 +8734,7 @@
         <v>20</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>81</v>
@@ -8759,10 +8754,10 @@
         <v>303</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8785,19 +8780,19 @@
         <v>82</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="P63" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="Q63" t="s" s="2">
         <v>20</v>
@@ -8846,7 +8841,7 @@
         <v>20</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>74</v>
@@ -8866,10 +8861,10 @@
         <v>303</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -8892,16 +8887,16 @@
         <v>82</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
@@ -8951,7 +8946,7 @@
         <v>20</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>74</v>
@@ -8971,14 +8966,14 @@
         <v>303</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
@@ -8997,19 +8992,19 @@
         <v>82</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O65" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="P65" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>20</v>
@@ -9058,7 +9053,7 @@
         <v>20</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>74</v>
@@ -9078,14 +9073,14 @@
         <v>303</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" t="s" s="2">
@@ -9104,19 +9099,19 @@
         <v>82</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O66" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="P66" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="Q66" t="s" s="2">
         <v>20</v>
@@ -9165,7 +9160,7 @@
         <v>20</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>74</v>
@@ -9185,10 +9180,10 @@
         <v>303</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9211,16 +9206,16 @@
         <v>82</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="O67" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -9270,7 +9265,7 @@
         <v>20</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>74</v>
@@ -9290,10 +9285,10 @@
         <v>303</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9316,17 +9311,17 @@
         <v>82</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="Q68" t="s" s="2">
         <v>20</v>
@@ -9375,7 +9370,7 @@
         <v>20</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>74</v>
@@ -9395,10 +9390,10 @@
         <v>303</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9421,19 +9416,19 @@
         <v>82</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="P69" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="Q69" t="s" s="2">
         <v>20</v>
@@ -9482,7 +9477,7 @@
         <v>20</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>74</v>
@@ -9491,7 +9486,7 @@
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>93</v>
@@ -9502,10 +9497,10 @@
         <v>303</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9531,16 +9526,16 @@
         <v>187</v>
       </c>
       <c r="M70" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="P70" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="Q70" t="s" s="2">
         <v>20</v>
@@ -9568,10 +9563,10 @@
         <v>191</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AA70" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB70" t="s" s="2">
         <v>20</v>
@@ -9589,7 +9584,7 @@
         <v>20</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>74</v>
@@ -9598,7 +9593,7 @@
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>93</v>
@@ -9609,14 +9604,14 @@
         <v>303</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" t="s" s="2">
@@ -9638,16 +9633,16 @@
         <v>187</v>
       </c>
       <c r="M71" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="P71" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="Q71" t="s" s="2">
         <v>20</v>
@@ -9675,10 +9670,10 @@
         <v>191</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AA71" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AB71" t="s" s="2">
         <v>20</v>
@@ -9696,7 +9691,7 @@
         <v>20</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>74</v>
@@ -9716,10 +9711,10 @@
         <v>303</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9742,19 +9737,19 @@
         <v>20</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="P72" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="Q72" t="s" s="2">
         <v>20</v>
@@ -9803,7 +9798,7 @@
         <v>20</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>74</v>
@@ -9823,10 +9818,10 @@
         <v>303</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9852,13 +9847,13 @@
         <v>187</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -9884,13 +9879,13 @@
         <v>20</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>368</v>
+        <v>436</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AA73" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AB73" t="s" s="2">
         <v>20</v>
@@ -9908,7 +9903,7 @@
         <v>20</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>74</v>
@@ -9928,10 +9923,10 @@
         <v>303</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -9957,16 +9952,16 @@
         <v>187</v>
       </c>
       <c r="M74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="P74" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="Q74" t="s" s="2">
         <v>20</v>
@@ -9991,13 +9986,13 @@
         <v>20</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>368</v>
+        <v>436</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AA74" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AB74" t="s" s="2">
         <v>20</v>
@@ -10015,7 +10010,7 @@
         <v>20</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>74</v>
@@ -10035,10 +10030,10 @@
         <v>303</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10061,16 +10056,16 @@
         <v>20</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" t="s" s="2">
@@ -10120,7 +10115,7 @@
         <v>20</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>74</v>
@@ -10140,10 +10135,10 @@
         <v>303</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10166,16 +10161,16 @@
         <v>20</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" t="s" s="2">
@@ -10225,7 +10220,7 @@
         <v>20</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>74</v>
@@ -10245,10 +10240,10 @@
         <v>303</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10274,16 +10269,16 @@
         <v>207</v>
       </c>
       <c r="M77" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="P77" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="Q77" t="s" s="2">
         <v>20</v>
@@ -10332,7 +10327,7 @@
         <v>20</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>74</v>
@@ -10344,7 +10339,7 @@
         <v>20</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="78">
@@ -10352,10 +10347,10 @@
         <v>303</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10455,10 +10450,10 @@
         <v>303</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10560,10 +10555,10 @@
         <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10667,10 +10662,10 @@
         <v>303</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10693,13 +10688,13 @@
         <v>20</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
@@ -10750,7 +10745,7 @@
         <v>20</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>74</v>
@@ -10759,7 +10754,7 @@
         <v>81</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>93</v>
@@ -10770,10 +10765,10 @@
         <v>303</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10796,13 +10791,13 @@
         <v>20</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
@@ -10853,7 +10848,7 @@
         <v>20</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>74</v>
@@ -10862,7 +10857,7 @@
         <v>81</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>93</v>
@@ -10873,10 +10868,10 @@
         <v>303</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -10902,16 +10897,16 @@
         <v>187</v>
       </c>
       <c r="M83" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O83" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="P83" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="Q83" t="s" s="2">
         <v>20</v>
@@ -10939,10 +10934,10 @@
         <v>105</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AA83" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AB83" t="s" s="2">
         <v>20</v>
@@ -10960,7 +10955,7 @@
         <v>20</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>74</v>
@@ -10980,10 +10975,10 @@
         <v>303</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11009,16 +11004,16 @@
         <v>187</v>
       </c>
       <c r="M84" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O84" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="P84" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="Q84" t="s" s="2">
         <v>20</v>
@@ -11043,13 +11038,13 @@
         <v>20</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>368</v>
+        <v>436</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AA84" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AB84" t="s" s="2">
         <v>20</v>
@@ -11067,7 +11062,7 @@
         <v>20</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>74</v>
@@ -11087,10 +11082,10 @@
         <v>303</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11113,17 +11108,17 @@
         <v>20</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q85" t="s" s="2">
         <v>20</v>
@@ -11172,7 +11167,7 @@
         <v>20</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>74</v>
@@ -11192,10 +11187,10 @@
         <v>303</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11221,10 +11216,10 @@
         <v>214</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -11275,7 +11270,7 @@
         <v>20</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>74</v>
@@ -11295,10 +11290,10 @@
         <v>303</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11321,16 +11316,16 @@
         <v>82</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P87" s="2"/>
       <c r="Q87" t="s" s="2">
@@ -11380,7 +11375,7 @@
         <v>20</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>74</v>
@@ -11400,10 +11395,10 @@
         <v>303</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11417,7 +11412,7 @@
         <v>75</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>20</v>
@@ -11426,16 +11421,16 @@
         <v>82</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
@@ -11485,7 +11480,7 @@
         <v>20</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>74</v>
@@ -11505,10 +11500,10 @@
         <v>303</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11534,16 +11529,16 @@
         <v>207</v>
       </c>
       <c r="M89" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O89" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="P89" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="Q89" t="s" s="2">
         <v>20</v>
@@ -11592,7 +11587,7 @@
         <v>20</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>74</v>
@@ -11612,10 +11607,10 @@
         <v>303</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11715,10 +11710,10 @@
         <v>303</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11820,10 +11815,10 @@
         <v>303</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11927,10 +11922,10 @@
         <v>303</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -11956,16 +11951,16 @@
         <v>187</v>
       </c>
       <c r="M93" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O93" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="N93" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="P93" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q93" t="s" s="2">
         <v>20</v>
@@ -11990,13 +11985,13 @@
         <v>20</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>368</v>
+        <v>436</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>369</v>
+        <v>517</v>
       </c>
       <c r="AA93" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AB93" t="s" s="2">
         <v>20</v>
@@ -12014,7 +12009,7 @@
         <v>20</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>81</v>
@@ -12034,10 +12029,10 @@
         <v>303</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12060,19 +12055,19 @@
         <v>82</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O94" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N94" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>522</v>
-      </c>
       <c r="P94" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="Q94" t="s" s="2">
         <v>20</v>
@@ -12121,7 +12116,7 @@
         <v>20</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>74</v>
@@ -12141,10 +12136,10 @@
         <v>303</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -12170,16 +12165,16 @@
         <v>187</v>
       </c>
       <c r="M95" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="O95" t="s" s="2">
-        <v>526</v>
-      </c>
       <c r="P95" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="Q95" t="s" s="2">
         <v>20</v>
@@ -12207,10 +12202,10 @@
         <v>191</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AA95" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB95" t="s" s="2">
         <v>20</v>
@@ -12228,7 +12223,7 @@
         <v>20</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>74</v>
@@ -12237,7 +12232,7 @@
         <v>81</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>93</v>
@@ -12248,14 +12243,14 @@
         <v>303</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s" s="2">
@@ -12277,16 +12272,16 @@
         <v>187</v>
       </c>
       <c r="M96" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="P96" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="Q96" t="s" s="2">
         <v>20</v>
@@ -12314,10 +12309,10 @@
         <v>191</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AA96" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AB96" t="s" s="2">
         <v>20</v>
@@ -12335,7 +12330,7 @@
         <v>20</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>74</v>
@@ -12355,10 +12350,10 @@
         <v>303</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12384,16 +12379,16 @@
         <v>76</v>
       </c>
       <c r="M97" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N97" t="s" s="2">
-        <v>530</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P97" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Q97" t="s" s="2">
         <v>20</v>
@@ -12442,7 +12437,7 @@
         <v>20</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>74</v>

--- a/temp/pages/all-profiles.xlsx
+++ b/temp/pages/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-27T11:31:10-04:00</t>
+    <t>2025-07-27T11:33:37-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1607,7 +1607,7 @@
     <t>(USCDI) US Core Profiles or other resource the observation is made from</t>
   </si>
   <si>
-    <t>Observations or or other resource such as a QuestionnaireResponse from which this observation value is derived.</t>
+    <t>Observations from which this observation value is derived.</t>
   </si>
   <si>
     <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>

--- a/temp/pages/all-profiles.xlsx
+++ b/temp/pages/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-27T11:33:37-04:00</t>
+    <t>2025-07-27T15:07:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="F69" s="2"/>
       <c r="G69" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>

--- a/temp/pages/all-profiles.xlsx
+++ b/temp/pages/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5231" uniqueCount="749">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-27T15:07:55-04:00</t>
+    <t>2025-07-28T11:44:01-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1688,6 +1688,687 @@
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>mh-toc-postpartum-summary</t>
+  </si>
+  <si>
+    <t>http://example.org/StructureDefinition/mh-toc-postpartum-summary</t>
+  </si>
+  <si>
+    <t>MHTOCPostpartumSummaryProfile</t>
+  </si>
+  <si>
+    <t>MH TOC Postpartum Summary Profile</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>DocumentReference</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-documentreference</t>
+  </si>
+  <si>
+    <t>A reference to a document</t>
+  </si>
+  <si>
+    <t>DocumentReference.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta</t>
+  </si>
+  <si>
+    <t>DocumentReference.implicitRules</t>
+  </si>
+  <si>
+    <t>DocumentReference.language</t>
+  </si>
+  <si>
+    <t>DocumentReference.text</t>
+  </si>
+  <si>
+    <t>DocumentReference.contained</t>
+  </si>
+  <si>
+    <t>DocumentReference.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.modifierExtension</t>
+  </si>
+  <si>
+    <t>DocumentReference.masterIdentifier</t>
+  </si>
+  <si>
+    <t>Master Version Specific Identifier</t>
+  </si>
+  <si>
+    <t>Document identifier as assigned by the source of the document. This identifier is specific to this version of the document. This unique identifier may be used elsewhere to identify this version of the document.</t>
+  </si>
+  <si>
+    <t>CDA Document Id extension and root.</t>
+  </si>
+  <si>
+    <t>The structure and format of this Id shall be consistent with the specification corresponding to the formatCode attribute. (e.g. for a DICOM standard document a 64-character numeric UID, for an HL7 CDA format a serialization of the CDA Document Id extension and root in the form "oid^extension", where OID is a 64 digits max, and the Id is a 16 UTF-8 char max. If the OID is coded without the extension then the '^' character shall not be included.).</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier</t>
+  </si>
+  <si>
+    <t>(USCDI) Other identifiers for the document</t>
+  </si>
+  <si>
+    <t>Other identifiers associated with the document, including version independent identifiers.</t>
+  </si>
+  <si>
+    <t>DocumentReference.status</t>
+  </si>
+  <si>
+    <t>(USCDI) current | superseded | entered-in-error</t>
+  </si>
+  <si>
+    <t>The status of this document reference.</t>
+  </si>
+  <si>
+    <t>This is the status of the DocumentReference object, which might be independent from the docStatus element.
+This element is labeled as a modifier because the status contains the codes that mark the document or reference as not currently valid.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/document-reference-status</t>
+  </si>
+  <si>
+    <t>DocumentReference.docStatus</t>
+  </si>
+  <si>
+    <t>preliminary | final | amended | entered-in-error</t>
+  </si>
+  <si>
+    <t>The status of the underlying document.</t>
+  </si>
+  <si>
+    <t>The document that is pointed to might be in various lifecycle states.</t>
+  </si>
+  <si>
+    <t>Status of the underlying document.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/composition-status|4.0.1</t>
+  </si>
+  <si>
+    <t>DocumentReference.type</t>
+  </si>
+  <si>
+    <t>(USCDI) Kind of document (LOINC if possible)</t>
+  </si>
+  <si>
+    <t>Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
+  </si>
+  <si>
+    <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v3-NullFlavor"/&gt;
+    &lt;code value="UNK"/&gt;
+    &lt;display value="unknown"/&gt;
+  &lt;/coding&gt;
+  &lt;text value="Postpartum Summary"/&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>All LOINC  values whose SCALE is DOC in the LOINC database and the HL7 v3 Code System NullFlavor concept 'unknown'</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-type</t>
+  </si>
+  <si>
+    <t>DocumentReference.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claxs
+</t>
+  </si>
+  <si>
+    <t>(USCDI) Categorization of document</t>
+  </si>
+  <si>
+    <t>A categorization for the type of document referenced - helps for indexing and searching. This may be implied by or derived from the code specified in the DocumentReference.type.</t>
+  </si>
+  <si>
+    <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
+  </si>
+  <si>
+    <t>High-level kind of a clinical document at a macro level.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+  </si>
+  <si>
+    <t>DocumentReference.category:uscore</t>
+  </si>
+  <si>
+    <t>uscore</t>
+  </si>
+  <si>
+    <t>The US Core DocumentReferences Type Value Set is a "starter set" of categories supported for fetching and storing clinical notes. Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-category</t>
+  </si>
+  <si>
+    <t>DocumentReference.subject</t>
+  </si>
+  <si>
+    <t>(USCDI) Who/what is the subject of the document</t>
+  </si>
+  <si>
+    <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
+  </si>
+  <si>
+    <t>DocumentReference.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indexed
+</t>
+  </si>
+  <si>
+    <t>(USCDI) When this document reference was created</t>
+  </si>
+  <si>
+    <t>When the document reference was created.</t>
+  </si>
+  <si>
+    <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
+  </si>
+  <si>
+    <t>DocumentReference.author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole)
+</t>
+  </si>
+  <si>
+    <t>(USCDI) Who and/or what authored the document</t>
+  </si>
+  <si>
+    <t>Identifies who is responsible for adding the information to the document.</t>
+  </si>
+  <si>
+    <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
+  </si>
+  <si>
+    <t>DocumentReference.authenticator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+</t>
+  </si>
+  <si>
+    <t>Who/what authenticated the document</t>
+  </si>
+  <si>
+    <t>Which person or organization authenticates that this document is valid.</t>
+  </si>
+  <si>
+    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
+  </si>
+  <si>
+    <t>DocumentReference.custodian</t>
+  </si>
+  <si>
+    <t>Organization which maintains the document</t>
+  </si>
+  <si>
+    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
+  </si>
+  <si>
+    <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo</t>
+  </si>
+  <si>
+    <t>Relationships to other documents</t>
+  </si>
+  <si>
+    <t>Relationships that this document has with other document references that already exist.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo.modifierExtension</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo.code</t>
+  </si>
+  <si>
+    <t>replaces | transforms | signs | appends</t>
+  </si>
+  <si>
+    <t>The type of relationship that this document has with anther document.</t>
+  </si>
+  <si>
+    <t>If this document appends another document, then the document cannot be fully understood without also accessing the referenced document.</t>
+  </si>
+  <si>
+    <t>The type of relationship between documents.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/document-relationship-type|4.0.1</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo.target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DocumentReference)
+</t>
+  </si>
+  <si>
+    <t>Target of the relationship</t>
+  </si>
+  <si>
+    <t>The target document of this relationship.</t>
+  </si>
+  <si>
+    <t>DocumentReference.description</t>
+  </si>
+  <si>
+    <t>Human-readable description</t>
+  </si>
+  <si>
+    <t>Human-readable description of the source document.</t>
+  </si>
+  <si>
+    <t>What the document is about,  a terse summary of the document.</t>
+  </si>
+  <si>
+    <t>Helps humans to assess whether the document is of interest.</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel</t>
+  </si>
+  <si>
+    <t>Document security-tags</t>
+  </si>
+  <si>
+    <t>A set of Security-Tag codes specifying the level of privacy/security of the Document. Note that DocumentReference.meta.security contains the security labels of the "reference" to the document, while DocumentReference.securityLabel contains a snapshot of the security labels on the document the reference refers to.</t>
+  </si>
+  <si>
+    <t>The confidentiality codes can carry multiple vocabulary items. HL7 has developed an understanding of security and privacy tags that might be desirable in a Document Sharing environment, called HL7 Healthcare Privacy and Security Classification System (HCS). The following specification is recommended but not mandated, as the vocabulary bindings are an administrative domain responsibility. The use of this method is up to the policy domain such as the XDS Affinity Domain or other Trust Domain where all parties including sender and recipients are trusted to appropriately tag and enforce.   
+In the HL7 Healthcare Privacy and Security Classification (HCS) there are code systems specific to Confidentiality, Sensitivity, Integrity, and Handling Caveats. Some values would come from a local vocabulary as they are related to workflow roles and special projects.</t>
+  </si>
+  <si>
+    <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>DocumentReference.content</t>
+  </si>
+  <si>
+    <t>(USCDI) Document referenced</t>
+  </si>
+  <si>
+    <t>The document and format referenced. There may be multiple content element repetitions, each with a different format.</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.modifierExtension</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment</t>
+  </si>
+  <si>
+    <t>(USCDI) Where to access the document</t>
+  </si>
+  <si>
+    <t>The document or URL of the document along with critical metadata to prove content has integrity.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+us-core-6:DocumentReference.content.attachment.url or DocumentReference.content.attachment.data or both SHALL be present. {url.exists() or data.exists()}</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.contentType</t>
+  </si>
+  <si>
+    <t>(USCDI) Mime type of the content, with charset etc.</t>
+  </si>
+  <si>
+    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
+  </si>
+  <si>
+    <t>Processors of the data need to be able to know how to interpret the data.</t>
+  </si>
+  <si>
+    <t>text/plain; charset=UTF-8, image/png</t>
+  </si>
+  <si>
+    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.contentType</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.language</t>
+  </si>
+  <si>
+    <t>Human language of the content (BCP-47)</t>
+  </si>
+  <si>
+    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
+  </si>
+  <si>
+    <t>Users need to be able to choose between the languages in a set of attachments.</t>
+  </si>
+  <si>
+    <t>en-AU</t>
+  </si>
+  <si>
+    <t>Attachment.language</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
+</t>
+  </si>
+  <si>
+    <t>(USCDI) Data inline, base64ed</t>
+  </si>
+  <si>
+    <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
+  </si>
+  <si>
+    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
+  </si>
+  <si>
+    <t>The data needs to able to be transmitted inline.</t>
+  </si>
+  <si>
+    <t>Attachment.data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">us-core-6
+</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>(USCDI) Uri where the data can be found</t>
+  </si>
+  <si>
+    <t>A location where the data can be accessed.</t>
+  </si>
+  <si>
+    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
+  </si>
+  <si>
+    <t>The data needs to be transmitted by reference.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/logo-small.png</t>
+  </si>
+  <si>
+    <t>Attachment.url</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Number of bytes of content (if url provided)</t>
+  </si>
+  <si>
+    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
+  </si>
+  <si>
+    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
+  </si>
+  <si>
+    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
+  </si>
+  <si>
+    <t>Attachment.size</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.hash</t>
+  </si>
+  <si>
+    <t>Hash of the data (sha-1, base64ed)</t>
+  </si>
+  <si>
+    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
+  </si>
+  <si>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+  </si>
+  <si>
+    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
+  </si>
+  <si>
+    <t>Attachment.hash</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.title</t>
+  </si>
+  <si>
+    <t>Label to display in place of the data</t>
+  </si>
+  <si>
+    <t>A label or set of text to display in place of the data.</t>
+  </si>
+  <si>
+    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
+  </si>
+  <si>
+    <t>Official Corporate Logo</t>
+  </si>
+  <si>
+    <t>Attachment.title</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date attachment was first created</t>
+  </si>
+  <si>
+    <t>The date that the attachment was first created.</t>
+  </si>
+  <si>
+    <t>This is often tracked as an integrity issue for use of the attachment.</t>
+  </si>
+  <si>
+    <t>Attachment.creation</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>(USCDI) Format/content rules for the document</t>
+  </si>
+  <si>
+    <t>An identifier of the document encoding, structure, and template that the document conforms to beyond the base format indicated in the mimeType.</t>
+  </si>
+  <si>
+    <t>Note that while IHE mostly issues URNs for format types, not all documents can be identified by a URI.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/formatcodes</t>
+  </si>
+  <si>
+    <t>DocumentReference.context</t>
+  </si>
+  <si>
+    <t>(USCDI) Clinical context of document</t>
+  </si>
+  <si>
+    <t>The clinical context in which the document was prepared.</t>
+  </si>
+  <si>
+    <t>These values are primarily added to help with searching for interesting/relevant documents.</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.modifierExtension</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-encounter)
+</t>
+  </si>
+  <si>
+    <t>(USCDI) Context of the document  content</t>
+  </si>
+  <si>
+    <t>Describes the clinical encounter or type of care that the document content is associated with.</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.event</t>
+  </si>
+  <si>
+    <t>Main clinical acts documented</t>
+  </si>
+  <si>
+    <t>This list of codes represents the main clinical acts, such as a colonoscopy or an appendectomy, being documented. In some cases, the event is inherent in the type Code, such as a "History and Physical Report" in which the procedure being documented is necessarily a "History and Physical" act.</t>
+  </si>
+  <si>
+    <t>An event can further specialize the act inherent in the type, such as  where it is simply "Procedure Report" and the procedure was a "colonoscopy". If one or more event codes are included, they shall not conflict with the values inherent in the class or type elements as such a conflict would create an ambiguous situation.</t>
+  </si>
+  <si>
+    <t>This list of codes represents the main clinical acts being documented.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.period</t>
+  </si>
+  <si>
+    <t>(USCDI) Time of service that is being documented</t>
+  </si>
+  <si>
+    <t>The time period over which the service that is described by the document was provided.</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.facilityType</t>
+  </si>
+  <si>
+    <t>Kind of facility where patient was seen</t>
+  </si>
+  <si>
+    <t>The kind of facility where the patient was seen.</t>
+  </si>
+  <si>
+    <t>XDS Facility Type.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.practiceSetting</t>
+  </si>
+  <si>
+    <t>Additional details about where the content was created (e.g. clinical specialty)</t>
+  </si>
+  <si>
+    <t>This property may convey specifics about the practice setting where the content was created, often reflecting the clinical specialty.</t>
+  </si>
+  <si>
+    <t>This element should be based on a coarse classification system for the class of specialty practice. Recommend the use of the classification system for Practice Setting, such as that described by the Subject Matter Domain in LOINC.</t>
+  </si>
+  <si>
+    <t>This is an important piece of metadata that providers often rely upon to quickly sort and/or filter out to find specific content.</t>
+  </si>
+  <si>
+    <t>Additional details about where the content was created (e.g. clinical specialty).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.sourcePatientInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient)
+</t>
+  </si>
+  <si>
+    <t>Patient demographics from source</t>
+  </si>
+  <si>
+    <t>The Patient Information as known when the document was published. May be a reference to a version specific, or contained.</t>
+  </si>
+  <si>
+    <t>DocumentReference.context.related</t>
+  </si>
+  <si>
+    <t>Related identifiers or resources</t>
+  </si>
+  <si>
+    <t>Related identifiers or resources associated with the DocumentReference.</t>
+  </si>
+  <si>
+    <t>May be identifiers or resources that caused the DocumentReference or referenced Document to be created.</t>
   </si>
 </sst>
 </file>
@@ -1821,7 +2502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -2150,6 +2831,168 @@
         <v>36</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -2157,12 +3000,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK97"/>
+  <dimension ref="A1:AK153"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="37.03125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="24.4921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="41.796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="33.17578125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.30078125" customWidth="true" bestFit="true"/>
@@ -2180,19 +3023,19 @@
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="42.890625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="30.83984375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="13.91796875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="148.8828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="248.53125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="59.63671875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="16.2578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="34.578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="13.54296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="36.45703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="8.22265625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
@@ -12452,6 +13295,5878 @@
         <v>93</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P98" s="2"/>
+      <c r="Q98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R98" s="2"/>
+      <c r="S98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="D99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F99" s="2"/>
+      <c r="G99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="P99" s="2"/>
+      <c r="Q99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R99" s="2"/>
+      <c r="S99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="D100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F100" s="2"/>
+      <c r="G100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R100" s="2"/>
+      <c r="S100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="D101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F101" s="2"/>
+      <c r="G101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="P101" s="2"/>
+      <c r="Q101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R101" s="2"/>
+      <c r="S101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="D102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F102" s="2"/>
+      <c r="G102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="P102" s="2"/>
+      <c r="Q102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R102" s="2"/>
+      <c r="S102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="D103" s="2"/>
+      <c r="E103" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F103" s="2"/>
+      <c r="G103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="P103" s="2"/>
+      <c r="Q103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R103" s="2"/>
+      <c r="S103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="D104" s="2"/>
+      <c r="E104" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F104" s="2"/>
+      <c r="G104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="P104" s="2"/>
+      <c r="Q104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R104" s="2"/>
+      <c r="S104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="D105" s="2"/>
+      <c r="E105" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F105" s="2"/>
+      <c r="G105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P105" s="2"/>
+      <c r="Q105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R105" s="2"/>
+      <c r="S105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="D106" s="2"/>
+      <c r="E106" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F106" s="2"/>
+      <c r="G106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="Q106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R106" s="2"/>
+      <c r="S106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="D107" s="2"/>
+      <c r="E107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F107" s="2"/>
+      <c r="G107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="Q107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R107" s="2"/>
+      <c r="S107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="D108" s="2"/>
+      <c r="E108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F108" s="2"/>
+      <c r="G108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" s="2"/>
+      <c r="Q108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R108" s="2"/>
+      <c r="S108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="D109" s="2"/>
+      <c r="E109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F109" s="2"/>
+      <c r="G109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P109" s="2"/>
+      <c r="Q109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R109" s="2"/>
+      <c r="S109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Z109" s="2"/>
+      <c r="AA109" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="D110" s="2"/>
+      <c r="E110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F110" s="2"/>
+      <c r="G110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="P110" s="2"/>
+      <c r="Q110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R110" s="2"/>
+      <c r="S110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="D111" s="2"/>
+      <c r="E111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F111" s="2"/>
+      <c r="G111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P111" s="2"/>
+      <c r="Q111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R111" s="2"/>
+      <c r="S111" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="D112" s="2"/>
+      <c r="E112" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="F112" s="2"/>
+      <c r="G112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="P112" s="2"/>
+      <c r="Q112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R112" s="2"/>
+      <c r="S112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AD112" s="2"/>
+      <c r="AE112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="E113" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="F113" s="2"/>
+      <c r="G113" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="P113" s="2"/>
+      <c r="Q113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R113" s="2"/>
+      <c r="S113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F114" s="2"/>
+      <c r="G114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" s="2"/>
+      <c r="Q114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R114" s="2"/>
+      <c r="S114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="D115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="F115" s="2"/>
+      <c r="G115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="P115" s="2"/>
+      <c r="Q115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R115" s="2"/>
+      <c r="S115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="D116" s="2"/>
+      <c r="E116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F116" s="2"/>
+      <c r="G116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="P116" s="2"/>
+      <c r="Q116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R116" s="2"/>
+      <c r="S116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="D117" s="2"/>
+      <c r="E117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F117" s="2"/>
+      <c r="G117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P117" s="2"/>
+      <c r="Q117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R117" s="2"/>
+      <c r="S117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="D118" s="2"/>
+      <c r="E118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F118" s="2"/>
+      <c r="G118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="P118" s="2"/>
+      <c r="Q118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R118" s="2"/>
+      <c r="S118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="D119" s="2"/>
+      <c r="E119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F119" s="2"/>
+      <c r="G119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="P119" s="2"/>
+      <c r="Q119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R119" s="2"/>
+      <c r="S119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="D120" s="2"/>
+      <c r="E120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F120" s="2"/>
+      <c r="G120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2"/>
+      <c r="Q120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R120" s="2"/>
+      <c r="S120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="D121" s="2"/>
+      <c r="E121" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F121" s="2"/>
+      <c r="G121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P121" s="2"/>
+      <c r="Q121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R121" s="2"/>
+      <c r="S121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="D122" s="2"/>
+      <c r="E122" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="F122" s="2"/>
+      <c r="G122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="Q122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R122" s="2"/>
+      <c r="S122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="D123" s="2"/>
+      <c r="E123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F123" s="2"/>
+      <c r="G123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="P123" s="2"/>
+      <c r="Q123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R123" s="2"/>
+      <c r="S123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="D124" s="2"/>
+      <c r="E124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F124" s="2"/>
+      <c r="G124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" s="2"/>
+      <c r="Q124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R124" s="2"/>
+      <c r="S124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="D125" s="2"/>
+      <c r="E125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F125" s="2"/>
+      <c r="G125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="Q125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R125" s="2"/>
+      <c r="S125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="D126" s="2"/>
+      <c r="E126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F126" s="2"/>
+      <c r="G126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="Q126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R126" s="2"/>
+      <c r="S126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="D127" s="2"/>
+      <c r="E127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F127" s="2"/>
+      <c r="G127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" s="2"/>
+      <c r="Q127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R127" s="2"/>
+      <c r="S127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="D128" s="2"/>
+      <c r="E128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F128" s="2"/>
+      <c r="G128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" s="2"/>
+      <c r="Q128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R128" s="2"/>
+      <c r="S128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="D129" s="2"/>
+      <c r="E129" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F129" s="2"/>
+      <c r="G129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P129" s="2"/>
+      <c r="Q129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R129" s="2"/>
+      <c r="S129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="D130" s="2"/>
+      <c r="E130" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="F130" s="2"/>
+      <c r="G130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="Q130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R130" s="2"/>
+      <c r="S130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="D131" s="2"/>
+      <c r="E131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F131" s="2"/>
+      <c r="G131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" s="2"/>
+      <c r="Q131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R131" s="2"/>
+      <c r="S131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="D132" s="2"/>
+      <c r="E132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F132" s="2"/>
+      <c r="G132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O132" s="2"/>
+      <c r="P132" s="2"/>
+      <c r="Q132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R132" s="2"/>
+      <c r="S132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="D133" s="2"/>
+      <c r="E133" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F133" s="2"/>
+      <c r="G133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P133" s="2"/>
+      <c r="Q133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R133" s="2"/>
+      <c r="S133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="D134" s="2"/>
+      <c r="E134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F134" s="2"/>
+      <c r="G134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="Q134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R134" s="2"/>
+      <c r="S134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="D135" s="2"/>
+      <c r="E135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F135" s="2"/>
+      <c r="G135" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="Q135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R135" s="2"/>
+      <c r="S135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="D136" s="2"/>
+      <c r="E136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F136" s="2"/>
+      <c r="G136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="Q136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R136" s="2"/>
+      <c r="S136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="D137" s="2"/>
+      <c r="E137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F137" s="2"/>
+      <c r="G137" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="P137" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="Q137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R137" s="2"/>
+      <c r="S137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="D138" s="2"/>
+      <c r="E138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F138" s="2"/>
+      <c r="G138" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="Q138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R138" s="2"/>
+      <c r="S138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="D139" s="2"/>
+      <c r="E139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F139" s="2"/>
+      <c r="G139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="P139" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="Q139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R139" s="2"/>
+      <c r="S139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="D140" s="2"/>
+      <c r="E140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F140" s="2"/>
+      <c r="G140" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="Q140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R140" s="2"/>
+      <c r="S140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="D141" s="2"/>
+      <c r="E141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F141" s="2"/>
+      <c r="G141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="Q141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R141" s="2"/>
+      <c r="S141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="D142" s="2"/>
+      <c r="E142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F142" s="2"/>
+      <c r="G142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="P142" s="2"/>
+      <c r="Q142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R142" s="2"/>
+      <c r="S142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Z142" s="2"/>
+      <c r="AA142" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="D143" s="2"/>
+      <c r="E143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F143" s="2"/>
+      <c r="G143" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="P143" s="2"/>
+      <c r="Q143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R143" s="2"/>
+      <c r="S143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="D144" s="2"/>
+      <c r="E144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F144" s="2"/>
+      <c r="G144" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O144" s="2"/>
+      <c r="P144" s="2"/>
+      <c r="Q144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R144" s="2"/>
+      <c r="S144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="D145" s="2"/>
+      <c r="E145" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F145" s="2"/>
+      <c r="G145" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P145" s="2"/>
+      <c r="Q145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R145" s="2"/>
+      <c r="S145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="D146" s="2"/>
+      <c r="E146" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="F146" s="2"/>
+      <c r="G146" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P146" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="Q146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R146" s="2"/>
+      <c r="S146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="D147" s="2"/>
+      <c r="E147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F147" s="2"/>
+      <c r="G147" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="O147" s="2"/>
+      <c r="P147" s="2"/>
+      <c r="Q147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R147" s="2"/>
+      <c r="S147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="C148" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="D148" s="2"/>
+      <c r="E148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F148" s="2"/>
+      <c r="G148" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="P148" s="2"/>
+      <c r="Q148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R148" s="2"/>
+      <c r="S148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="C149" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="D149" s="2"/>
+      <c r="E149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F149" s="2"/>
+      <c r="G149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="O149" s="2"/>
+      <c r="P149" s="2"/>
+      <c r="Q149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R149" s="2"/>
+      <c r="S149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="D150" s="2"/>
+      <c r="E150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F150" s="2"/>
+      <c r="G150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="O150" s="2"/>
+      <c r="P150" s="2"/>
+      <c r="Q150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R150" s="2"/>
+      <c r="S150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="C151" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="D151" s="2"/>
+      <c r="E151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F151" s="2"/>
+      <c r="G151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="P151" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="Q151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R151" s="2"/>
+      <c r="S151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="D152" s="2"/>
+      <c r="E152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F152" s="2"/>
+      <c r="G152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="O152" s="2"/>
+      <c r="P152" s="2"/>
+      <c r="Q152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R152" s="2"/>
+      <c r="S152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="C153" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="D153" s="2"/>
+      <c r="E153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F153" s="2"/>
+      <c r="G153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="P153" s="2"/>
+      <c r="Q153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R153" s="2"/>
+      <c r="S153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
